--- a/Bitacora.xlsx
+++ b/Bitacora.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyecto Peluquería\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9179B722-F9C5-49FB-AF73-C7445BE9A097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4886A783-510B-47E6-B817-BE49042FB70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{32B2A248-DEC6-4912-BC2D-428943FB5A8B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="97">
   <si>
     <t>RF</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Probado/ok</t>
   </si>
   <si>
-    <t>NOMBRE DEL RF</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cliente crea su propia cuenta </t>
   </si>
   <si>
@@ -141,9 +138,6 @@
     <t>RF - 14</t>
   </si>
   <si>
-    <t>RF - 15</t>
-  </si>
-  <si>
     <t>RF - 16</t>
   </si>
   <si>
@@ -229,6 +223,108 @@
   </si>
   <si>
     <t>PUT /citas/:idcita/reprogramar</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>RF - 18</t>
+  </si>
+  <si>
+    <t>RF - 19</t>
+  </si>
+  <si>
+    <t>RF - 20</t>
+  </si>
+  <si>
+    <t>RF - 21</t>
+  </si>
+  <si>
+    <t>PUT /usuario/desactivar/:idcliente</t>
+  </si>
+  <si>
+    <t>Admin activa cliente</t>
+  </si>
+  <si>
+    <t>Admin activa trabajador</t>
+  </si>
+  <si>
+    <t>Admin desactiva cliente</t>
+  </si>
+  <si>
+    <t>Admin desactiva trabajador</t>
+  </si>
+  <si>
+    <t>Cliente desactiva su cuenta</t>
+  </si>
+  <si>
+    <t>RF - 22</t>
+  </si>
+  <si>
+    <t>Admin inicia sesión</t>
+  </si>
+  <si>
+    <t>POST /seguridad/login</t>
+  </si>
+  <si>
+    <t>RUTA</t>
+  </si>
+  <si>
+    <t>RF - 15.1</t>
+  </si>
+  <si>
+    <t>RF - 15.2</t>
+  </si>
+  <si>
+    <t>vista/admin/RutasAdmin.js</t>
+  </si>
+  <si>
+    <t>vista/clientes/RutasClientes.js</t>
+  </si>
+  <si>
+    <t>vista/Trabajadores/RutasTrabajadores.js</t>
+  </si>
+  <si>
+    <t>vista/horarios/RutasHorarios.js</t>
+  </si>
+  <si>
+    <t>vista/citas/RutasCitas.js</t>
+  </si>
+  <si>
+    <t>RF - 23</t>
+  </si>
+  <si>
+    <t>RF - 24</t>
+  </si>
+  <si>
+    <t>Admin desactiva admin</t>
+  </si>
+  <si>
+    <t>Admin activa admin</t>
+  </si>
+  <si>
+    <t>PUT /seguridad/desactivaradmin/:id</t>
+  </si>
+  <si>
+    <t>PUT /seguridad/activaradmin/:id</t>
+  </si>
+  <si>
+    <t>PUT /seguridad/activarcliente/:id</t>
+  </si>
+  <si>
+    <t>PUT /seguridad/desactivarcliente/:id</t>
+  </si>
+  <si>
+    <t>PUT /seguridad/activartrabajador/:id</t>
+  </si>
+  <si>
+    <t>PUT /seguridad/desactivartrabajador/:id</t>
+  </si>
+  <si>
+    <t>RF - 25</t>
+  </si>
+  <si>
+    <t>Admin elimina admin</t>
   </si>
 </sst>
 </file>
@@ -697,410 +793,665 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D27FAA5-B765-4C56-9E45-8C66F9D32997}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.54296875" style="1"/>
-    <col min="2" max="2" width="40.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="41.90625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.08984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7265625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="36.54296875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="C6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="D7" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="G7" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="D8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="G8" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="D9" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="G9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>45</v>
-      </c>
       <c r="D10" s="10" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G10" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G11" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G12" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C14" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="D16" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="8" t="s">
+      <c r="D17" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="4" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="G19" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="4" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="C20" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="G20" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="D21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="G23" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="4" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="4" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>16</v>
-      </c>
+      <c r="G24" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F3"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G3"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Bitacora.xlsx
+++ b/Bitacora.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyecto Peluquería\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4886A783-510B-47E6-B817-BE49042FB70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990FF374-9CF1-4F2D-8112-206ED5DA1696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{32B2A248-DEC6-4912-BC2D-428943FB5A8B}"/>
   </bookViews>

--- a/Bitacora.xlsx
+++ b/Bitacora.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyecto Peluquería\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990FF374-9CF1-4F2D-8112-206ED5DA1696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C43F168-8016-4C8C-A236-743EE35ABDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{32B2A248-DEC6-4912-BC2D-428943FB5A8B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="98">
   <si>
     <t>RF</t>
   </si>
@@ -168,9 +168,6 @@
     <t>GET /horarios</t>
   </si>
   <si>
-    <t>GET /seguridad/horarios</t>
-  </si>
-  <si>
     <t>GET /trabajador/horarios/:idtrabajador</t>
   </si>
   <si>
@@ -325,6 +322,12 @@
   </si>
   <si>
     <t>Admin elimina admin</t>
+  </si>
+  <si>
+    <t>GET /seguridad/horarios/:idtrabajador</t>
+  </si>
+  <si>
+    <t>DELETE /seguridad/admins/:idadmin</t>
   </si>
 </sst>
 </file>
@@ -807,7 +810,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -818,7 +821,7 @@
     </row>
     <row r="2" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -841,19 +844,19 @@
         <v>0</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>1</v>
@@ -870,7 +873,7 @@
         <v>38</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>3</v>
@@ -893,7 +896,7 @@
         <v>39</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>3</v>
@@ -916,7 +919,7 @@
         <v>40</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>3</v>
@@ -939,7 +942,7 @@
         <v>41</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>3</v>
@@ -962,7 +965,7 @@
         <v>42</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>3</v>
@@ -986,7 +989,7 @@
         <v>43</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>3</v>
@@ -1006,10 +1009,10 @@
         <v>12</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>3</v>
@@ -1029,10 +1032,10 @@
         <v>13</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>3</v>
@@ -1052,10 +1055,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>3</v>
@@ -1075,10 +1078,10 @@
         <v>10</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>3</v>
@@ -1098,10 +1101,10 @@
         <v>14</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>3</v>
@@ -1121,10 +1124,10 @@
         <v>19</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>3</v>
@@ -1144,10 +1147,10 @@
         <v>36</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>3</v>
@@ -1167,10 +1170,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>3</v>
@@ -1184,16 +1187,16 @@
     </row>
     <row r="19" spans="1:7" s="4" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="D19" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>3</v>
@@ -1207,16 +1210,16 @@
     </row>
     <row r="20" spans="1:7" s="4" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>3</v>
@@ -1236,10 +1239,10 @@
         <v>35</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>3</v>
@@ -1253,16 +1256,16 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="D22" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>3</v>
@@ -1276,16 +1279,16 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>3</v>
@@ -1299,16 +1302,16 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>3</v>
@@ -1322,16 +1325,16 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>3</v>
@@ -1345,16 +1348,16 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>3</v>
@@ -1368,16 +1371,16 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>3</v>
@@ -1391,16 +1394,16 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>3</v>
@@ -1414,16 +1417,16 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>3</v>
@@ -1437,16 +1440,26 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="C30" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Bitacora.xlsx
+++ b/Bitacora.xlsx
@@ -8,13 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyecto Peluquería\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C43F168-8016-4C8C-A236-743EE35ABDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D33263E-87AA-4D6A-9579-511E00F02A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{32B2A248-DEC6-4912-BC2D-428943FB5A8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Bitacora" sheetId="1" r:id="rId1"/>
+    <sheet name="Admin" sheetId="2" r:id="rId2"/>
+    <sheet name="Clientes" sheetId="3" r:id="rId3"/>
+    <sheet name="Trabajadores" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Bitacora!$A$4:$I$30</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="98">
   <si>
     <t>RF</t>
   </si>
@@ -1470,4 +1476,854 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16DFCD1A-F746-4B56-97DF-F78FFF992B06}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{743A508E-2EF4-42BE-9C7C-94DCD368F7B6}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.6328125" customWidth="1"/>
+    <col min="2" max="2" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" customWidth="1"/>
+    <col min="6" max="6" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D86890-1F3B-4EEB-9EF3-F1FC130C3C63}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bitacora.xlsx
+++ b/Bitacora.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyecto Peluquería\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D33263E-87AA-4D6A-9579-511E00F02A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4658F9D6-753A-4498-8602-0F340CECF34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{32B2A248-DEC6-4912-BC2D-428943FB5A8B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="98">
   <si>
     <t>RF</t>
   </si>
@@ -2296,29 +2296,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
+    <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
